--- a/worked_examples/AIHE-CASE03B_hospital_command_dashboard_and_patient_flow/workbook/xlsx/AIHE-CASE03B_worked_example_and_template.xlsx
+++ b/worked_examples/AIHE-CASE03B_hospital_command_dashboard_and_patient_flow/workbook/xlsx/AIHE-CASE03B_worked_example_and_template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R31b3efbbb3c14976"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R3e3a2be65ead4bb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Analysis" sheetId="3" r:id="R4188c6fee5524cbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="R46cc18ecbfba4823"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="5" r:id="R21b5405a33f84a5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="Rc1a85a5bb14b47f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R43cc9c720c7e4c0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Analysis" sheetId="3" r:id="R1d82376bf11a4b8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="R46b45bd557c14535"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="5" r:id="Rd36f7b290a494fb5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,7 +20,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -43,8 +43,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF303236"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -61,6 +67,16 @@
         <x:fgColor rgb="FFEDE3E6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6B2230"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F0E7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="18">
     <x:border/>
@@ -173,18 +189,18 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="83">
+  <x:cellXfs count="93">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre"/>
+      <x:alignment/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre"/>
+      <x:alignment/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -192,7 +208,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -200,30 +216,30 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -249,42 +265,42 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -371,6 +387,34 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -380,7 +424,7 @@
   <x:dxfs count="1">
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF8D7DA"/>
         </x:patternFill>
       </x:fill>
@@ -401,25 +445,26 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:rPr/>
               <a:t>Pressure score by operational interval</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:v>Pressure score</c:v>
           </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:strRef>
               <c:f>'Decision Summary'!$M$3:$M$8</c:f>
@@ -437,7 +482,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -542,7 +586,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Racb04d45d206427d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb9604c5915aa415e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -632,9 +676,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -743,17 +787,17 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="83" t="str">
         <x:v>AIHE-CASE03B — Hospital Command Dashboard and Patient Flow</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
+      <x:c r="B1" s="83"/>
+      <x:c r="C1" s="83"/>
+      <x:c r="D1" s="83"/>
+      <x:c r="E1" s="83"/>
+      <x:c r="F1" s="83"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="16" t="str">
+      <x:c r="A3" s="85" t="str">
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B3" s="28" t="str">
@@ -761,7 +805,7 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="18" t="str">
+      <x:c r="A4" s="87" t="str">
         <x:v>Chapter</x:v>
       </x:c>
       <x:c r="B4" s="29" t="str">
@@ -769,7 +813,7 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="18" t="str">
+      <x:c r="A5" s="87" t="str">
         <x:v>Decision question</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
@@ -777,7 +821,7 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="18" t="str">
+      <x:c r="A6" s="87" t="str">
         <x:v>Use</x:v>
       </x:c>
       <x:c r="B6" s="29" t="str">
@@ -785,7 +829,7 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="18" t="str">
+      <x:c r="A7" s="87" t="str">
         <x:v>Interpretation</x:v>
       </x:c>
       <x:c r="B7" s="29" t="str">
@@ -793,7 +837,7 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="18" t="str">
+      <x:c r="A8" s="87" t="str">
         <x:v>Governance</x:v>
       </x:c>
       <x:c r="B8" s="29" t="str">
@@ -801,7 +845,7 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="18" t="str">
+      <x:c r="A9" s="87" t="str">
         <x:v>Data protection</x:v>
       </x:c>
       <x:c r="B9" s="29" t="str">
@@ -809,7 +853,7 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="18" t="str">
+      <x:c r="A10" s="87" t="str">
         <x:v>Status</x:v>
       </x:c>
       <x:c r="B10" s="29" t="str">
@@ -817,7 +861,7 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="20" t="str">
+      <x:c r="A11" s="89" t="str">
         <x:v>Related resources</x:v>
       </x:c>
       <x:c r="B11" s="30" t="str">
@@ -842,13 +886,13 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="42" t="str">
+      <x:c r="A1" s="90" t="str">
         <x:v>Parameter</x:v>
       </x:c>
-      <x:c r="B1" s="43" t="str">
+      <x:c r="B1" s="91" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C1" s="44" t="str">
+      <x:c r="C1" s="92" t="str">
         <x:v>Interpretation</x:v>
       </x:c>
     </x:row>
@@ -943,7 +987,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ca06668a79d4aaf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0397a9e5aa5e4f37"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -974,61 +1018,61 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="42" t="str">
+      <x:c r="A1" s="90" t="str">
         <x:v>Interval</x:v>
       </x:c>
-      <x:c r="B1" s="43" t="str">
+      <x:c r="B1" s="91" t="str">
         <x:v>Forecast arrivals</x:v>
       </x:c>
-      <x:c r="C1" s="43" t="str">
+      <x:c r="C1" s="91" t="str">
         <x:v>Actual arrivals</x:v>
       </x:c>
-      <x:c r="D1" s="43" t="str">
+      <x:c r="D1" s="91" t="str">
         <x:v>Staffed beds</x:v>
       </x:c>
-      <x:c r="E1" s="43" t="str">
+      <x:c r="E1" s="91" t="str">
         <x:v>Occupied beds</x:v>
       </x:c>
-      <x:c r="F1" s="43" t="str">
+      <x:c r="F1" s="91" t="str">
         <x:v>Planned discharges</x:v>
       </x:c>
-      <x:c r="G1" s="43" t="str">
+      <x:c r="G1" s="91" t="str">
         <x:v>Completed discharges</x:v>
       </x:c>
-      <x:c r="H1" s="43" t="str">
+      <x:c r="H1" s="91" t="str">
         <x:v>Imaging queue</x:v>
       </x:c>
-      <x:c r="I1" s="43" t="str">
+      <x:c r="I1" s="91" t="str">
         <x:v>Transport delay (min)</x:v>
       </x:c>
-      <x:c r="J1" s="43" t="str">
+      <x:c r="J1" s="91" t="str">
         <x:v>Nursing gap (FTE)</x:v>
       </x:c>
-      <x:c r="K1" s="43" t="str">
+      <x:c r="K1" s="91" t="str">
         <x:v>Action latency (min)</x:v>
       </x:c>
-      <x:c r="L1" s="43" t="str">
+      <x:c r="L1" s="91" t="str">
         <x:v>Boarded patients</x:v>
       </x:c>
-      <x:c r="M1" s="43" t="str">
+      <x:c r="M1" s="91" t="str">
         <x:v>Recorded action</x:v>
       </x:c>
-      <x:c r="N1" s="43" t="str">
+      <x:c r="N1" s="91" t="str">
         <x:v>Occupancy rate</x:v>
       </x:c>
-      <x:c r="O1" s="43" t="str">
+      <x:c r="O1" s="91" t="str">
         <x:v>Absolute forecast error</x:v>
       </x:c>
-      <x:c r="P1" s="43" t="str">
+      <x:c r="P1" s="91" t="str">
         <x:v>Discharge completion rate</x:v>
       </x:c>
-      <x:c r="Q1" s="43" t="str">
+      <x:c r="Q1" s="91" t="str">
         <x:v>Pressure score</x:v>
       </x:c>
-      <x:c r="R1" s="43" t="str">
+      <x:c r="R1" s="91" t="str">
         <x:v>Timely action</x:v>
       </x:c>
-      <x:c r="S1" s="44" t="str">
+      <x:c r="S1" s="92" t="str">
         <x:v>Pressure level</x:v>
       </x:c>
     </x:row>
@@ -1442,7 +1486,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15886785b7ce435a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3063823f53254433"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1456,25 +1500,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="83" t="str">
         <x:v>Worked decision summary</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
+      <x:c r="B1" s="83"/>
+      <x:c r="C1" s="83"/>
+      <x:c r="D1" s="83"/>
+      <x:c r="E1" s="83"/>
+      <x:c r="F1" s="83"/>
     </x:row>
     <x:row r="2">
-      <x:c r="M2" s="42" t="str">
+      <x:c r="M2" s="90" t="str">
         <x:v>Interval</x:v>
       </x:c>
-      <x:c r="N2" s="44" t="str">
+      <x:c r="N2" s="92" t="str">
         <x:v>Pressure score</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="16" t="str">
+      <x:c r="A3" s="85" t="str">
         <x:v>Average occupancy</x:v>
       </x:c>
       <x:c r="B3" s="79" t="n">
@@ -1491,7 +1535,7 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="18" t="str">
+      <x:c r="A4" s="87" t="str">
         <x:v>Mean absolute arrival error</x:v>
       </x:c>
       <x:c r="B4" s="29" t="n">
@@ -1508,7 +1552,7 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="18" t="str">
+      <x:c r="A5" s="87" t="str">
         <x:v>Average discharge completion</x:v>
       </x:c>
       <x:c r="B5" s="81" t="n">
@@ -1525,7 +1569,7 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="18" t="str">
+      <x:c r="A6" s="87" t="str">
         <x:v>Timely-action proportion</x:v>
       </x:c>
       <x:c r="B6" s="29" t="n">
@@ -1542,7 +1586,7 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="18" t="str">
+      <x:c r="A7" s="87" t="str">
         <x:v>Maximum pressure score</x:v>
       </x:c>
       <x:c r="B7" s="29" t="n">
@@ -1559,7 +1603,7 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="18" t="str">
+      <x:c r="A8" s="87" t="str">
         <x:v>High-pressure intervals</x:v>
       </x:c>
       <x:c r="B8" s="29" t="n">
@@ -1576,7 +1620,7 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="20" t="str">
+      <x:c r="A9" s="89" t="str">
         <x:v>Worked recommendation</x:v>
       </x:c>
       <x:c r="B9" s="30" t="str">
@@ -1588,7 +1632,7 @@
     <x:mergeCell ref="A1:F1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc26b572b383f49c6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd855d74c673f432c"/>
 </x:worksheet>
 </file>
 
@@ -1618,61 +1662,61 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="42" t="str">
+      <x:c r="A1" s="90" t="str">
         <x:v>Interval</x:v>
       </x:c>
-      <x:c r="B1" s="43" t="str">
+      <x:c r="B1" s="91" t="str">
         <x:v>Forecast arrivals</x:v>
       </x:c>
-      <x:c r="C1" s="43" t="str">
+      <x:c r="C1" s="91" t="str">
         <x:v>Actual arrivals</x:v>
       </x:c>
-      <x:c r="D1" s="43" t="str">
+      <x:c r="D1" s="91" t="str">
         <x:v>Staffed beds</x:v>
       </x:c>
-      <x:c r="E1" s="43" t="str">
+      <x:c r="E1" s="91" t="str">
         <x:v>Occupied beds</x:v>
       </x:c>
-      <x:c r="F1" s="43" t="str">
+      <x:c r="F1" s="91" t="str">
         <x:v>Planned discharges</x:v>
       </x:c>
-      <x:c r="G1" s="43" t="str">
+      <x:c r="G1" s="91" t="str">
         <x:v>Completed discharges</x:v>
       </x:c>
-      <x:c r="H1" s="43" t="str">
+      <x:c r="H1" s="91" t="str">
         <x:v>Imaging queue</x:v>
       </x:c>
-      <x:c r="I1" s="43" t="str">
+      <x:c r="I1" s="91" t="str">
         <x:v>Transport delay (min)</x:v>
       </x:c>
-      <x:c r="J1" s="43" t="str">
+      <x:c r="J1" s="91" t="str">
         <x:v>Nursing gap (FTE)</x:v>
       </x:c>
-      <x:c r="K1" s="43" t="str">
+      <x:c r="K1" s="91" t="str">
         <x:v>Action latency (min)</x:v>
       </x:c>
-      <x:c r="L1" s="43" t="str">
+      <x:c r="L1" s="91" t="str">
         <x:v>Boarded patients</x:v>
       </x:c>
-      <x:c r="M1" s="43" t="str">
+      <x:c r="M1" s="91" t="str">
         <x:v>Recorded action</x:v>
       </x:c>
-      <x:c r="N1" s="43" t="str">
+      <x:c r="N1" s="91" t="str">
         <x:v>Occupancy rate</x:v>
       </x:c>
-      <x:c r="O1" s="43" t="str">
+      <x:c r="O1" s="91" t="str">
         <x:v>Absolute forecast error</x:v>
       </x:c>
-      <x:c r="P1" s="43" t="str">
+      <x:c r="P1" s="91" t="str">
         <x:v>Discharge completion rate</x:v>
       </x:c>
-      <x:c r="Q1" s="43" t="str">
+      <x:c r="Q1" s="91" t="str">
         <x:v>Pressure score</x:v>
       </x:c>
-      <x:c r="R1" s="43" t="str">
+      <x:c r="R1" s="91" t="str">
         <x:v>Timely action</x:v>
       </x:c>
-      <x:c r="S1" s="44" t="str">
+      <x:c r="S1" s="92" t="str">
         <x:v>Pressure level</x:v>
       </x:c>
     </x:row>
@@ -1699,9 +1743,8 @@
       <x:c r="P2" s="75" t="str">
         <x:f>IFERROR(G2/F2,"")</x:f>
       </x:c>
-      <x:c r="Q2" s="56" t="n">
+      <x:c r="Q2" s="56" t="str">
         <x:f>IF(COUNTA(A2:M2)=0,"",ROUND(N2*Parameters!$B$2+L2*Parameters!$B$3+H2*Parameters!$B$4+I2*Parameters!$B$5+J2*Parameters!$B$6,1))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="R2" s="56" t="str">
         <x:f>IF(K2="","",IF(K2&lt;=Parameters!$B$7,"Yes","No"))</x:f>
@@ -1733,9 +1776,8 @@
       <x:c r="P3" s="75" t="str">
         <x:f>IFERROR(G3/F3,"")</x:f>
       </x:c>
-      <x:c r="Q3" s="56" t="n">
+      <x:c r="Q3" s="56" t="str">
         <x:f>IF(COUNTA(A3:M3)=0,"",ROUND(N3*Parameters!$B$2+L3*Parameters!$B$3+H3*Parameters!$B$4+I3*Parameters!$B$5+J3*Parameters!$B$6,1))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="R3" s="56" t="str">
         <x:f>IF(K3="","",IF(K3&lt;=Parameters!$B$7,"Yes","No"))</x:f>
@@ -1767,9 +1809,8 @@
       <x:c r="P4" s="75" t="str">
         <x:f>IFERROR(G4/F4,"")</x:f>
       </x:c>
-      <x:c r="Q4" s="56" t="n">
+      <x:c r="Q4" s="56" t="str">
         <x:f>IF(COUNTA(A4:M4)=0,"",ROUND(N4*Parameters!$B$2+L4*Parameters!$B$3+H4*Parameters!$B$4+I4*Parameters!$B$5+J4*Parameters!$B$6,1))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="R4" s="56" t="str">
         <x:f>IF(K4="","",IF(K4&lt;=Parameters!$B$7,"Yes","No"))</x:f>
@@ -1801,9 +1842,8 @@
       <x:c r="P5" s="75" t="str">
         <x:f>IFERROR(G5/F5,"")</x:f>
       </x:c>
-      <x:c r="Q5" s="56" t="n">
+      <x:c r="Q5" s="56" t="str">
         <x:f>IF(COUNTA(A5:M5)=0,"",ROUND(N5*Parameters!$B$2+L5*Parameters!$B$3+H5*Parameters!$B$4+I5*Parameters!$B$5+J5*Parameters!$B$6,1))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="R5" s="56" t="str">
         <x:f>IF(K5="","",IF(K5&lt;=Parameters!$B$7,"Yes","No"))</x:f>
@@ -1835,9 +1875,8 @@
       <x:c r="P6" s="75" t="str">
         <x:f>IFERROR(G6/F6,"")</x:f>
       </x:c>
-      <x:c r="Q6" s="56" t="n">
+      <x:c r="Q6" s="56" t="str">
         <x:f>IF(COUNTA(A6:M6)=0,"",ROUND(N6*Parameters!$B$2+L6*Parameters!$B$3+H6*Parameters!$B$4+I6*Parameters!$B$5+J6*Parameters!$B$6,1))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="R6" s="56" t="str">
         <x:f>IF(K6="","",IF(K6&lt;=Parameters!$B$7,"Yes","No"))</x:f>
@@ -1869,9 +1908,8 @@
       <x:c r="P7" s="75" t="str">
         <x:f>IFERROR(G7/F7,"")</x:f>
       </x:c>
-      <x:c r="Q7" s="56" t="n">
+      <x:c r="Q7" s="56" t="str">
         <x:f>IF(COUNTA(A7:M7)=0,"",ROUND(N7*Parameters!$B$2+L7*Parameters!$B$3+H7*Parameters!$B$4+I7*Parameters!$B$5+J7*Parameters!$B$6,1))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="R7" s="56" t="str">
         <x:f>IF(K7="","",IF(K7&lt;=Parameters!$B$7,"Yes","No"))</x:f>
@@ -1903,9 +1941,8 @@
       <x:c r="P8" s="75" t="str">
         <x:f>IFERROR(G8/F8,"")</x:f>
       </x:c>
-      <x:c r="Q8" s="56" t="n">
+      <x:c r="Q8" s="56" t="str">
         <x:f>IF(COUNTA(A8:M8)=0,"",ROUND(N8*Parameters!$B$2+L8*Parameters!$B$3+H8*Parameters!$B$4+I8*Parameters!$B$5+J8*Parameters!$B$6,1))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="R8" s="56" t="str">
         <x:f>IF(K8="","",IF(K8&lt;=Parameters!$B$7,"Yes","No"))</x:f>
@@ -1937,9 +1974,8 @@
       <x:c r="P9" s="75" t="str">
         <x:f>IFERROR(G9/F9,"")</x:f>
       </x:c>
-      <x:c r="Q9" s="56" t="n">
+      <x:c r="Q9" s="56" t="str">
         <x:f>IF(COUNTA(A9:M9)=0,"",ROUND(N9*Parameters!$B$2+L9*Parameters!$B$3+H9*Parameters!$B$4+I9*Parameters!$B$5+J9*Parameters!$B$6,1))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="R9" s="56" t="str">
         <x:f>IF(K9="","",IF(K9&lt;=Parameters!$B$7,"Yes","No"))</x:f>
@@ -1971,9 +2007,8 @@
       <x:c r="P10" s="75" t="str">
         <x:f>IFERROR(G10/F10,"")</x:f>
       </x:c>
-      <x:c r="Q10" s="56" t="n">
+      <x:c r="Q10" s="56" t="str">
         <x:f>IF(COUNTA(A10:M10)=0,"",ROUND(N10*Parameters!$B$2+L10*Parameters!$B$3+H10*Parameters!$B$4+I10*Parameters!$B$5+J10*Parameters!$B$6,1))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="R10" s="56" t="str">
         <x:f>IF(K10="","",IF(K10&lt;=Parameters!$B$7,"Yes","No"))</x:f>
@@ -2005,9 +2040,8 @@
       <x:c r="P11" s="75" t="str">
         <x:f>IFERROR(G11/F11,"")</x:f>
       </x:c>
-      <x:c r="Q11" s="56" t="n">
+      <x:c r="Q11" s="56" t="str">
         <x:f>IF(COUNTA(A11:M11)=0,"",ROUND(N11*Parameters!$B$2+L11*Parameters!$B$3+H11*Parameters!$B$4+I11*Parameters!$B$5+J11*Parameters!$B$6,1))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="R11" s="56" t="str">
         <x:f>IF(K11="","",IF(K11&lt;=Parameters!$B$7,"Yes","No"))</x:f>
@@ -2039,9 +2073,8 @@
       <x:c r="P12" s="75" t="str">
         <x:f>IFERROR(G12/F12,"")</x:f>
       </x:c>
-      <x:c r="Q12" s="56" t="n">
+      <x:c r="Q12" s="56" t="str">
         <x:f>IF(COUNTA(A12:M12)=0,"",ROUND(N12*Parameters!$B$2+L12*Parameters!$B$3+H12*Parameters!$B$4+I12*Parameters!$B$5+J12*Parameters!$B$6,1))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="R12" s="56" t="str">
         <x:f>IF(K12="","",IF(K12&lt;=Parameters!$B$7,"Yes","No"))</x:f>
@@ -2073,9 +2106,8 @@
       <x:c r="P13" s="76" t="str">
         <x:f>IFERROR(G13/F13,"")</x:f>
       </x:c>
-      <x:c r="Q13" s="58" t="n">
+      <x:c r="Q13" s="58" t="str">
         <x:f>IF(COUNTA(A13:M13)=0,"",ROUND(N13*Parameters!$B$2+L13*Parameters!$B$3+H13*Parameters!$B$4+I13*Parameters!$B$5+J13*Parameters!$B$6,1))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="R13" s="58" t="str">
         <x:f>IF(K13="","",IF(K13&lt;=Parameters!$B$7,"Yes","No"))</x:f>
